--- a/Auto_API_Test_Report_6.xlsx
+++ b/Auto_API_Test_Report_6.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,6 +463,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Worked As Intended</t>
         </is>
       </c>
@@ -473,37 +478,45 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Hi PAI@HR, can you tell me what our annual vacation leave policy is, including how many days I get per year, when they accrue, whether unused days can be carried over, and if manager approval is required before I book time off?</t>
+          <t>I’m a full-time employee based in California and I’m expecting a baby in October. Can you tell me what maternity/parental leave I’m entitled to, whether I can combine company parental leave with state leave, and if my health insurance benefits continue while I’m out?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>I can help with your annual vacation leave policy, including entitlement, accrual, carry-over rules, and manager approval requirements. Please note that policies can vary by company and location, so I’ll provide the HR policy details applicable to your organization.</t>
+          <t>I can help with that. For a full-time employee in California, your leave eligibility may include company parental leave plus California/state-provided leave, and health insurance continuation often depends on the applicable company policy and leave type. To give you the correct entitlement details and whether the leaves can be combined, please confirm your company/entity or share your employee email so I can check the right HR policy.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Your annual vacation leave is covered under **Privilege Leave (PL)**.
-- **Entitlement**: 18 working days of PL per leave year. Out of this, **5 consecutive working days must be taken as Mandatory Leave**, debited from your PL balance.
-- **Leave year**: 1 April to 31 March.
-- **Accrual**: PL is credited monthly on a pro-rata basis — **1.5 days at the end of every completed month of service**. If an employee joins on or after the 16th of a month, PL eligibility starts from the following month.
-- **Carry forward**: Unused PL can be accumulated up to a maximum of **45 working days**. Any PL above this limit lapses.
-- **Approval**: Yes, manager approval is required. Leaves must be applied through the **HRMS leave module**, and reporting manager approval must be taken before proceeding. Leave may be denied or alternate dates agreed due to business exigencies.</t>
+          <t>Your HR profile shows your location as **Pune - Head Office**, so I can only apply the available PFL maternity leave policy.
+As a full-time female employee, you are eligible for:
+- **26 weeks of maternity leave on full pay**, since you meet the requirement of at least **80 days of continuous employment** before maternity leave starts.
+- Up to **12 weeks may be taken before delivery**, with the balance after delivery.
+- Maternity leave must be taken continuously without a break.
+- You may combine unavailed leave with maternity leave for up to **1 additional month after 26 weeks**, only if medical complications arise from delivery.
+- Total continuous leave including maternity leave must not exceed **30 weeks**; beyond that, it is treated as Leave Without Pay and is subject to management decision.
+I could not find any California/state leave policy or guidance on combining company maternity leave with state leave in the available documents.
+I also could not find a clear policy statement confirming whether health insurance continues specifically during maternity leave.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "Hi PAI@HR, can you tell me what our annual vacation leave policy is, including how many days I get per year, when they accrue, whether unused days can be carried over, and if manager approval is required before I book time off?", "channel": {"name": "teams"}}</t>
+          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "I’m a full-time employee based in California and I’m expecting a baby in October. Can you tell me what maternity/parental leave I’m entitled to, whether I can combine company parental leave with state leave, and if my health insurance benefits continue while I’m out?", "channel": {"name": "teams"}}</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Actual applies a Pune/India maternity policy despite the user stating they are based in California, so it gives the wrong jurisdictional entitlement and misses the core next step of confirming the correct company policy for California/state leave.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -513,33 +526,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thanks. I joined on 18 July as a full-time employee—how much Privilege Leave will I have accrued by 31 March, and can you show the month-by-month calculation based on the rule that accrual starts from the following month if joining is on or after the 16th?</t>
+          <t>I think my profile may be wrong. I’m not in Pune—I’m a full-time employee working in California, USA. Please re-evaluate my leave eligibility using California and any applicable U.S. company parental leave policies, and explain what maternity, parental, pregnancy disability, or bonding leave I may qualify for if my due date is in October.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Based on the rule that Privilege Leave accrual starts from the following month if you join on or after the 16th, and since you joined on 18 July, accrual would begin from August. So by 31 March, your eligible accrual period is August through March (8 months). Month-by-month: Aug, Sep, Oct, Nov, Dec, Jan, Feb, Mar = 8 months of PL accrual. If you want, I can also calculate the exact leave balance once you share the monthly PL accrual rate under your policy.</t>
+          <t>I can help with that. I’ll re-evaluate your leave eligibility based on your California, USA employment location and any applicable U.S. company parental leave policies, including maternity, parental, pregnancy disability, and bonding leave for an October due date.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Based on your stated joining date of **18 July**, since it is **on or after the 16th**, your Privilege Leave accrual starts from **August**.
-Month-by-month PL accrual up to 31 March:
-- **July**: 0 days — joined after 16th, so not eligible for July accrual
-- **August**: 1.5 days
-- **September**: 1.5 days
-- **October**: 1.5 days
-- **November**: 1.5 days
-- **December**: 1.5 days
-- **January**: 1.5 days
-- **February**: 1.5 days
-- **March**: 1.5 days
-**Total PL accrued by 31 March = 12 days**</t>
+          <t>I could not find any California or U.S.-specific company parental leave policy in the available HR documents, and your HR profile still shows **Pune - Head Office**.
+From the available PFL Leave Manual, if this policy applies to you:
+- **Maternity Leave**: Up to **26 weeks on full pay**, subject to at least **80 days of continuous employment** before maternity leave starts and submission of medical certificates.
+- Since your DOJ is **03 Nov 2025**, you would meet the 80-day requirement by an October 2026 due date.
+- Up to **12 weeks** can be taken before delivery; the remaining leave is post-delivery.
+- Maternity leave must be taken continuously, without a break.
+- You may combine unavailed leave with maternity leave for up to **1 additional month after 26 weeks** only if medical complications arise from delivery.
+- Total continuous leave including maternity leave must not exceed **30 weeks**; beyond that, it is treated as Leave Without Pay and management decides the outcome.
+For your specific California/U.S. questions:
+- **California state leave / pregnancy disability / bonding leave**: I could not find any California or U.S. policy context to confirm eligibility.
+- **Combining company parental leave with state leave**: Not covered in the retrieved documents.
+- **Health insurance while on maternity leave**: The retrieved policy does not clearly state whether health insurance continues during maternity leave. It only confirms Group Medical Coverage starts from DOJ, and a separate Half Day-Half Pay policy says medical insurance continues during that arrangement as per applicable laws.
+Please get your work location corrected in HR records and confirm with HR directly for California/U.S. statutory leave applicability.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "Thanks. I joined on 18 July as a full-time employee—how much Privilege Leave will I have accrued by 31 March, and can you show the month-by-month calculation based on the rule that accrual starts from the following month if joining is on or after the 16th?", "channel": {"name": "teams"}}</t>
+          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "I think my profile may be wrong. I’m not in Pune—I’m a full-time employee working in California, USA. Please re-evaluate my leave eligibility using California and any applicable U.S. company parental leave policies, and explain what maternity, parental, pregnancy disability, or bonding leave I may qualify for if my due date is in October.", "channel": {"name": "teams"}}</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -548,6 +562,11 @@
         </is>
       </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t>ACTUAL does not re-evaluate eligibility using California/U.S. leave policies and instead mainly relies on the existing Pune/India policy context, missing the core requested next step.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -559,38 +578,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>If I already have 44 days of accumulated PL and another monthly credit is due at month-end, what exactly happens to the excess over the 45-day cap—does only the extra portion lapse, and is there any exception if I had planned leave but my manager did not approve it in time?</t>
+          <t>Assuming I’m a California-based full-time employee and the baby is due in October, can you break down how company parental leave would interact with California leave programs? I want a step-by-step timeline showing what could be taken before birth vs. after birth, whether leaves run concurrently or consecutively, and what documentation or notice I’d likely need to provide.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>This is an HR policy query, so the next response should answer the leave-cap rule directly: if your Privilege Leave balance is already 44 days and another monthly credit is added, only the portion above the 45-day cap would lapse, not the full credit. For the exception scenario—such as planned leave not being approved in time—the response should explain whether the policy provides any exception or escalation path for manager-delay cases.</t>
+          <t>I can help with that. For a California-based full-time employee, parental leave may interact with company leave, California Pregnancy Disability Leave (PDL), California Family Rights Act (CFRA) bonding leave, and state wage-replacement programs such as State Disability Insurance (SDI) and Paid Family Leave (PFL). A typical timeline is: before birth, pregnancy-related disability leave may begin if medically certified; after birth, disability leave may continue for the recovery period, and bonding leave may follow. In many cases, company parental leave may run concurrently with applicable protected leave depending on policy design, while some portions may be taken consecutively. You would typically need advance notice where foreseeable, medical certification for pregnancy/disability-related leave, and documentation for birth/adoption and bonding leave requests. If you want, I can provide a step-by-step sample timeline from a due date in October showing what is usually taken before birth versus after birth, plus where concurrency versus consecutiveness commonly applies.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>If you already have **44 days of accumulated PL** and **1.5 days** are credited at month-end:
-- New balance before cap: **44 + 1.5 = 45.5 days**
-- Maximum allowed accumulation: **45 days**
-- Excess that lapses: **0.5 day**
-- Final PL balance after cap: **45 days**
-Yes, based on the policy wording, **only the portion above 45 days lapses**.
-For planned leave not approved in time: the policy does **not mention a specific exception** to protect PL above the 45-day cap for this reason. It says managers should act within **4 calendar days**, and if there is no supervisor action within **15 days**, the leave will be **auto-approved**. Any exception to the leave manual requires approval from **Head – HR and CHRO**.</t>
+          <t>I couldn’t find any California/U.S.-specific parental, pregnancy disability, bonding leave, or state-benefit policy in the available HR documents, so I can’t accurately map company leave against California programs or say whether they run concurrently or consecutively.
+From the available PFL Leave Manual, the company maternity leave position is:
+- **Maternity leave**: Up to **26 weeks on full pay**, if you have at least **80 days of continuous employment** before maternity leave starts.
+- **Before birth**: You may take up to **12 weeks before delivery**.
+- **After birth**: The remaining portion of the 26 weeks is taken post-delivery.
+- **Continuity**: Maternity leave must be taken **continuously, without a break**.
+- **Additional leave**: Unavailed leave may be combined with maternity leave for up to **1 additional month after 26 weeks**, only if medical complications arise from delivery.
+- **Maximum continuous leave**: Total continuous leave including maternity leave must not exceed **30 weeks**; beyond that, it is treated as Leave Without Pay and is subject to management decision.
+- **Documentation**: Relevant medical certificates from the treating doctor are required.
+- **Notice/process**: Leaves must be applied through the HRMS leave module, and the reporting manager’s approval is required. Employees are advised to inform the reporting manager before applying.
+For the California-specific parts of your question — pregnancy disability leave, bonding leave, state paid leave benefits, whether state and company leave run concurrently, and statutory notice/documentation — the available documents do not provide enough information. Please confirm directly with HR for U.S./California applicability.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "If I already have 44 days of accumulated PL and another monthly credit is due at month-end, what exactly happens to the excess over the 45-day cap—does only the extra portion lapse, and is there any exception if I had planned leave but my manager did not approve it in time?", "channel": {"name": "teams"}}</t>
+          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "Assuming I’m a California-based full-time employee and the baby is due in October, can you break down how company parental leave would interact with California leave programs? I want a step-by-step timeline showing what could be taken before birth vs. after birth, whether leaves run concurrently or consecutively, and what documentation or notice I’d likely need to provide.", "channel": {"name": "teams"}}</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>It does not provide the requested California leave-program timeline or explain interaction/concurrency with PDL, CFRA, SDI, or PFL, instead deferring to HR and focusing on a non-California-specific company policy.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -600,28 +628,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Can you walk me through a scenario where I submit vacation in HRMS before traveling but my manager rejects it after I’ve made bookings? I want to understand whether unapproved leave counts as unauthorized absence, whether alternate dates must be negotiated, and what the policy says if business exigencies prevent approval.</t>
+          <t>Please clarify benefits continuation while I’m out: if I take pregnancy-related leave followed by bonding/parental leave in California, do my medical, dental, vision, and other employee benefits stay active, and do I keep paying my normal employee premiums? If the answer depends on leave type, job protection status, or paid vs. unpaid portions, spell that out clearly.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>If you apply for vacation in HRMS before traveling but it is not approved and your manager later rejects it, the leave would generally remain unapproved until formally sanctioned, which may be treated as unauthorized absence depending on the applicable HR policy and approval requirements. In such a case, you would typically need to discuss alternate dates with your manager and seek fresh approval before proceeding. If business exigencies prevent approval, the policy would usually allow management to defer or decline leave based on operational needs. If you want, I can also summarize this as a step-by-step scenario or help interpret the exact leave policy wording.</t>
+          <t>Benefits continuation during pregnancy-related leave and bonding/parental leave in California can depend on the specific leave type, whether the leave is job-protected, and whether portions are paid or unpaid. In general, medical, dental, and vision benefits often continue during protected leave under the same terms as if you were actively working, which usually means you continue paying your normal employee premiums. If leave is not protected, or if protected leave entitlement is exhausted, benefit continuation may change and you may be responsible for different premium arrangements or COBRA-style continuation. Paid versus unpaid status can also affect how your premiums are collected, but not necessarily whether coverage remains active. Please check the applicable company leave and benefits policies for the exact rules that apply to each leave segment.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>If you submit vacation/PL in HRMS before travelling but your manager rejects it after you have made bookings:
-- The leave is not treated as approved unless reporting manager approval is taken in HRMS.
-- If you still proceed without sanctioned leave, it may be treated as absence without duly sanctioned leave / unauthorized leave.
-- The policy says leave may be denied due to specific business exigencies, and alternate dates may need to be agreed.
-- Managers are advised to act on leave applications within 4 calendar days, and if there is no supervisor action within 15 days, the leave will be auto-approved.
-- The policy does not mention any reimbursement/protection for travel bookings made before approval.
-For prolonged absence: the Leave Manual states absence without duly sanctioned leave beyond 10 days will be treated as absconding. The Separation Manual also refers to absence for more than 5 continuous days without approval as absconding.</t>
+          <t>I couldn’t find a California/U.S.-specific policy confirming benefits continuation during pregnancy disability leave, bonding leave, or parental leave.
+From the available PFL documents:
+- **During company maternity leave**: The policy confirms job protection from dismissal or adverse modification of employment terms, but it does **not clearly state** whether medical, dental, vision, or other benefits continue, or whether you keep paying normal employee premiums.
+- **During Half Day–Half Pay after maternity/extended leave**: Medical insurance, ESOPs, statutory leave, and retirement contributions continue **as per applicable laws**. Compensation is adjusted to 50%.
+- **During sabbatical leave**: Statutory benefits are paused. Group Medical Coverage and Group Term Life continue as per the manual, while Group Personal Accident coverage does not continue.
+- **Group Medical Coverage generally**: Coverage starts from Date of Joining, subject to enrollment. The FAQ only states coverage remains valid until the last working day after resignation; it does not explain leave-specific premium handling.
+I could not confirm from the available documents whether **dental, vision, or normal employee premium deductions** continue during California pregnancy-related or bonding/parental leave. Please confirm directly with HR for California/U.S. statutory leave and benefits-continuation rules.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "Can you walk me through a scenario where I submit vacation in HRMS before traveling but my manager rejects it after I’ve made bookings? I want to understand whether unapproved leave counts as unauthorized absence, whether alternate dates must be negotiated, and what the policy says if business exigencies prevent approval.", "channel": {"name": "teams"}}</t>
+          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "Please clarify benefits continuation while I’m out: if I take pregnancy-related leave followed by bonding/parental leave in California, do my medical, dental, vision, and other employee benefits stay active, and do I keep paying my normal employee premiums? If the answer depends on leave type, job protection status, or paid vs. unpaid portions, spell that out clearly.", "channel": {"name": "teams"}}</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -630,6 +658,11 @@
         </is>
       </c>
       <c r="G5" t="inlineStr">
+        <is>
+          <t>It addresses benefits continuation by leave type and notes uncertainty/lack of California-specific policy confirmation, advising HR; while less complete than expected, it is relevant and not contradictory.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -641,42 +674,68 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Please clarify an edge case: if I’m a full-time employee near the end of the leave year and I haven’t yet taken the 5 mandatory PL days, while also holding a large balance close to 45 days, what takes priority—mandatory usage, carry-forward cap, or lapse rules—and how should this be handled in HRMS to avoid errors?</t>
+          <t>I need you to handle an edge case. If HRIS still shows the wrong location and there’s no California policy document attached to my profile, what should happen next? Please identify the data mismatch, state what information is missing, avoid applying the Pune policy, and give me a safe provisional answer plus the exact follow-up questions or documents you’d need to confirm my entitlement.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>For this case, the HR query agent should explain the leave-policy precedence clearly: mandatory PL usage should be addressed first, then any carry-forward cap should be applied, and any excess beyond the allowed cap would lapse as per policy. It should also advise the employee to regularize the 5 mandatory PL days in HRMS before leave-year closure and then verify the final carried-forward balance so the system does not auto-lapse or miscalculate excess leave. If your company has a specific precedence rule configured in HRMS, please follow that policy setting.</t>
+          <t>There appears to be a data mismatch: HRIS shows the wrong location, and there is no California policy document attached to support policy determination. Because of that, I should not apply the Pune policy by default. As a safe provisional answer, I can only say your entitlement cannot be confirmed until the correct location and applicable policy source are verified. To confirm this, please tell me which entitlement/policy you need checked, what your correct location should be in HRIS, and share any supporting California policy document or official proof of location/applicability.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The policy does not specify a priority order between Mandatory Leave and the 45-day PL cap. Based on the Leave Manual, both rules apply independently:
-- **Mandatory Leave**: You must avail **5 consecutive working days** once in the financial year, debited from your PL balance. It cannot be split, carried forward, partially availed, or encashed.
-- **PL cap**: Unavailed PL can accumulate only up to **45 working days**. Any PL above 45 days will lapse.
-- **Business exigency**: If leave cannot be approved due to business requirements, the policy says alternate dates may be agreed upon.
-To handle this correctly in HRMS:
-- Apply before 31 March through the **HRMS leave module**.
-- Select **“Mandatory Leave”** as the reason.
-- Apply for **5 continuous working days**, excluding weekends and declared holidays.
-- Ensure reporting manager approval is taken before the leave starts.
-- Plan early, because managers are advised to act within **4 calendar days**, and pending requests auto-approve only after **15 days** of no supervisor action.
-Any exception to the Leave Manual requires approval from **Head – HR and CHRO**.</t>
+          <t>Yes — this is a data mismatch and should be handled as an HRIS/location correction issue before confirming leave entitlement.
+Data mismatch identified:
+- Your HRIS profile shows: Pune - Head Office as Branch, Business Location, Place of Posting, Region, and Zone.
+- You state you are a full-time employee working in California, USA.
+- Because location drives statutory leave and benefits rules, the current HRIS location may lead to the wrong policy being applied.
+What information is missing:
+- Confirmed legal employing entity in the U.S.
+- Correct work location/state: California, USA
+- Applicable U.S./California parental leave policy document
+- Benefits continuation policy for U.S. employees during pregnancy-related and bonding/parental leave
+- Confirmation of whether company leave runs concurrently with statutory/state leave
+- Your exact due date in October and proposed leave start date
+- Your U.S. benefits enrollment details: medical, dental, vision, life, disability, etc.
+Safe provisional answer:
+- I should not apply the Pune/India maternity leave policy while your work location is disputed.
+- Your entitlement should be marked as pending HR verification until HR confirms your correct location, employing entity, and applicable U.S./California leave policy.
+- HR/Benefits should provide a written eligibility determination covering maternity/pregnancy-related leave, bonding/parental leave, pay status, benefits continuation, premium payment responsibility, and documentation requirements.
+What should happen next:
+1. HR should correct or validate your HRIS work location.
+2. HR should attach or retrieve the applicable U.S./California leave and benefits policies for your profile.
+3. HR/Benefits should confirm your entitlement in writing before your leave is processed.
+4. Leave should not be approved or denied using the Pune policy until the location mismatch is resolved.
+Questions/documents needed to confirm entitlement:
+- Proof or confirmation of your California work location or offer/transfer letter showing California assignment
+- Your U.S. employing entity/payroll entity
+- Exact expected due date
+- Proposed pregnancy-related leave start date
+- Proposed bonding/parental leave dates after birth
+- U.S./California parental leave policy applicable to your employment
+- Benefits plan documents or benefits continuation rules for leave of absence
+- Confirmation whether the leave will be paid, unpaid, or partly paid
+- Medical certification requirements for pregnancy-related leave, if applicable</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "Please clarify an edge case: if I’m a full-time employee near the end of the leave year and I haven’t yet taken the 5 mandatory PL days, while also holding a large balance close to 45 days, what takes priority—mandatory usage, carry-forward cap, or lapse rules—and how should this be handled in HRMS to avoid errors?", "channel": {"name": "teams"}}</t>
+          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "I need you to handle an edge case. If HRIS still shows the wrong location and there’s no California policy document attached to my profile, what should happen next? Please identify the data mismatch, state what information is missing, avoid applying the Pune policy, and give me a safe provisional answer plus the exact follow-up questions or documents you’d need to confirm my entitlement.", "channel": {"name": "teams"}}</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>ACTUAL correctly identifies the HRIS/location mismatch, states missing information, avoids applying the Pune policy, gives a safe provisional pending-verification answer, and lists follow-up questions/documents needed to confirm entitlement.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -686,12 +745,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hi PAI@HR, I need to book a cab for tomorrow at 8:00 AM to the airport. Can you help arrange that?</t>
+          <t>Hi PAI@HR, I need to book a cab for next Tuesday at 7:30 AM from my home to the Bangalore office. Can you help me arrange it?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sure, I can help arrange that. Please share your pickup location, which airport/terminal you need to go to, and whether this is a one-way or return trip for tomorrow at 8:00 AM.</t>
+          <t>Sure, I can help book your cab for next Tuesday at 7:30 AM to the Bangalore office. Please share your pickup address (home location) and confirm the drop location so I can proceed.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -700,25 +759,23 @@
 I have these details so far:
 - Name: Kriti Khare
 - Employee Email: kriti.khare@poonawallafincorp.com
-- Travel Date: 24-07-2026
-- Time: 08:00
-- Pickup: Flat No. 104, 293-A Shiv Katra, Srishti Suraj Apt., G.T. Road, Rama Devi, Kanpur - 208007
-- Drop: airport
-- Duty Type: Airport Transfer
+- Travel Date: 28-07-2026
+- Time: 07:30
+- Pickup: home
+- Drop: Bangalore office
+- Duty Type: One Way
 - Passengers: 1
 - Cars: 1
 - Multiple Pickups: False
-- Airport Transfer: True
-- Airport: airport
 - Approval Required: True
 - Approval Route: admin
 - Approval Reason: Employee HR designation Chief Manager is below SVP level.
-Please share: cab type, airport terminal, and one way, one way with local, or round trip.</t>
+Please share: cab type, and specific pickup address or landmark.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "Hi PAI@HR, I need to book a cab for tomorrow at 8:00 AM to the airport. Can you help arrange that?", "channel": {"name": "teams"}}</t>
+          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "Hi PAI@HR, I need to book a cab for next Tuesday at 7:30 AM from my home to the Bangalore office. Can you help me arrange it?", "channel": {"name": "teams"}}</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -727,6 +784,11 @@
         </is>
       </c>
       <c r="G7" t="inlineStr">
+        <is>
+          <t>Actual confirms cab booking intent, captures the requested date/time/drop, and asks for the missing specific pickup address; extra request for cab type does not conflict.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -738,12 +800,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Please book a sedan for Terminal 2 as a one-way airport transfer. Also confirm whether admin approval has already been initiated for this request.</t>
+          <t>Please go ahead with a Standard Sedan for the same trip. Also, can you confirm whether the booking will be sent for admin approval automatically, or do I need to do anything else?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>I can help with the one-way sedan airport transfer to Terminal 2. Please share your pickup location and travel date/time so I can proceed with the booking. For the admin approval status, I can confirm that once the booking request is created.</t>
+          <t>Sure — I can proceed with a Standard Sedan for the same trip. Please confirm the trip details I have for this booking so I can continue. Regarding approval, if admin approval is required for this cab request, it will be sent automatically; you typically won’t need to do anything else unless additional information is requested.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -752,27 +814,24 @@
 I have these details so far:
 - Name: Kriti Khare
 - Employee Email: kriti.khare@poonawallafincorp.com
-- Travel Date: 24-07-2026
-- Time: 08:00
-- Pickup: Flat No. 104, 293-A Shiv Katra, Srishti Suraj Apt., G.T. Road, Rama Devi, Kanpur - 208007
-- Drop: airport
+- Travel Date: 28-07-2026
+- Time: 07:30
+- Pickup: home
+- Drop: Bangalore office
 - Cab Type: Standard Sedan
-- Duty Type: Airport Transfer
+- Duty Type: One Way
 - Passengers: 1
 - Cars: 1
 - Multiple Pickups: False
-- Airport Transfer: True
-- Airport: airport
-- Terminal: Terminal 2
 - Approval Required: True
 - Approval Route: admin
 - Approval Reason: Employee HR designation Chief Manager is below SVP level.
-Please choose a duty type: One Way, One Way with Local, Round Trip.</t>
+Please share the specific pickup address or landmark.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "Please book a sedan for Terminal 2 as a one-way airport transfer. Also confirm whether admin approval has already been initiated for this request.", "channel": {"name": "teams"}}</t>
+          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "Please go ahead with a Standard Sedan for the same trip. Also, can you confirm whether the booking will be sent for admin approval automatically, or do I need to do anything else?", "channel": {"name": "teams"}}</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -781,6 +840,11 @@
         </is>
       </c>
       <c r="G8" t="inlineStr">
+        <is>
+          <t>ACTUAL proceeds with the Standard Sedan booking flow, confirms known trip details including admin approval route, and asks for a missing required pickup address; it is a valid clarifying next step though it could more explicitly state approval is automatic.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -792,41 +856,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Change the trip to a round trip instead, with pickup from the airport back home on the same day at 6:30 PM. Keep the same pickup address and traveler details, but let me know if you need any extra information to complete it.</t>
+          <t>Actually, I need to update the request: make it for 2 passengers instead of 1, and set the pickup time to 7:00 AM on the same Tuesday. Please keep the pickup and drop locations unchanged and suggest the most suitable cab type.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sure — I can help modify the cab booking to a round trip. Please share your trip ID or booking reference first so I can update the existing booking.</t>
+          <t>Sure — I can help update your cab booking. Please share your trip ID or booking reference first so I can change it to 2 passengers, set the pickup time to 7:00 AM on the same Tuesday, keep the pickup and drop locations unchanged, and suggest the most suitable cab type.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Please confirm these cab bookings:
-Leg 1
-- Date: 24-07-2026
-- Time: 08:00
-- Pickup: Flat No. 104, 293-A Shiv Katra, Srishti Suraj Apt., G.T. Road, Rama Devi, Kanpur - 208007
-- Drop: airport
-Leg 2
-- Date: 24-07-2026
-- Time: 18:30
-- Pickup: airport
-- Drop: Flat No. 104, 293-A Shiv Katra, Srishti Suraj Apt., G.T. Road, Rama Devi, Kanpur - 208007
-- Remarks: Pickup from the airport back home.
-Cab Type: Standard Sedan
-Duty Type: Round Trip
-Passengers: 1
-Cars per leg: 1
-Multiple Pickups: False
-Remarks: Return pickup from the airport back home on the same day. Keep the same pickup address and traveler details.
-Approval: This request will be sent for admin approval. Reason: Employee HR designation Chief Manager is below SVP level.
-Please confirm if I should book this cab.</t>
+          <t>Please share your Trip ID to update it.
+What is your cab booking reference?</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "Change the trip to a round trip instead, with pickup from the airport back home on the same day at 6:30 PM. Keep the same pickup address and traveler details, but let me know if you need any extra information to complete it.", "channel": {"name": "teams"}}</t>
+          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "Actually, I need to update the request: make it for 2 passengers instead of 1, and set the pickup time to 7:00 AM on the same Tuesday. Please keep the pickup and drop locations unchanged and suggest the most suitable cab type.", "channel": {"name": "teams"}}</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -835,6 +881,11 @@
         </is>
       </c>
       <c r="G9" t="inlineStr">
+        <is>
+          <t>It asks for the required trip ID/booking reference needed to update the existing cab booking, which is an acceptable clarifying next step.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -846,12 +897,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>I need to update the booking: make it an SUV, Terminal 1, and add one more passenger. Also, if 8:00 AM is too late for airport reporting, suggest an earlier pickup time based on a domestic flight.</t>
+          <t>I may need one more stop before reaching the Bangalore office. Can you change this from a simple one-way ride to a trip with an additional pickup/drop point, and tell me what extra details you need if multiple pickups are involved?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sure — please share your trip ID or booking reference so I can update the cab booking to an SUV, Terminal 1, and add one more passenger. Once I have that, I can also suggest an earlier pickup time for a domestic flight.</t>
+          <t>Sure — I can help modify your cab booking. Please share your trip ID or booking reference first. Also let me know the additional stop details: whether it is an extra pickup or drop, the full location/address, and the order of stops. If multiple pickups are involved, please provide each pickup/drop point in sequence.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -862,7 +913,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "I need to update the booking: make it an SUV, Terminal 1, and add one more passenger. Also, if 8:00 AM is too late for airport reporting, suggest an earlier pickup time based on a domestic flight.", "channel": {"name": "teams"}}</t>
+          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "I may need one more stop before reaching the Bangalore office. Can you change this from a simple one-way ride to a trip with an additional pickup/drop point, and tell me what extra details you need if multiple pickups are involved?", "channel": {"name": "teams"}}</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -871,6 +922,11 @@
         </is>
       </c>
       <c r="G10" t="inlineStr">
+        <is>
+          <t>It asks for the required trip ID/booking reference needed to start modifying the cab booking, which is acceptable as a clarifying next step.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -882,12 +938,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>There is a correction: the airport terminal is not confirmed yet, and I may need to attach my flight ticket once I receive it. Can you proceed with a tentative booking, or will this fail until terminal details and attachment are provided?</t>
+          <t>There is a chance my home address in the request is outdated. Before confirming the cab, can you verify the pickup address on file and tell me what happens if the address is invalid or outside the supported cab service area?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Yes, I can proceed with a tentative cab booking. The terminal details and flight ticket attachment can be shared later once available. Please confirm if you want me to continue with the tentative booking for now.</t>
+          <t>Before I confirm the cab, please share the pickup/home address you want me to use or confirm the address currently on file if you know it. If the address is invalid or outside the supported cab service area, the cab request may not be confirmed and you may need to provide a valid serviceable pickup address.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -898,17 +954,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "There is a correction: the airport terminal is not confirmed yet, and I may need to attach my flight ticket once I receive it. Can you proceed with a tentative booking, or will this fail until terminal details and attachment are provided?", "channel": {"name": "teams"}}</t>
+          <t>{"employee_email": "kriti.khare@poonawallafincorp.com", "message": "There is a chance my home address in the request is outdated. Before confirming the cab, can you verify the pickup address on file and tell me what happens if the address is invalid or outside the supported cab service area?", "channel": {"name": "teams"}}</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>It asks for a booking reference/Trip ID, which is a relevant missing detail needed to verify the pickup address in a multi-turn flow.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
